--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>1397000</v>
+        <v>1388000</v>
       </c>
       <c r="C419" t="n">
-        <v>601736</v>
+        <v>867373</v>
       </c>
       <c r="D419" t="n">
-        <v>1310183</v>
+        <v>1310647</v>
       </c>
       <c r="E419" t="n">
-        <v>1384779</v>
+        <v>1384447</v>
       </c>
       <c r="F419" t="n">
-        <v>1357954</v>
+        <v>1359003</v>
       </c>
       <c r="G419" t="n">
-        <v>1350972</v>
+        <v>1351366</v>
       </c>
       <c r="H419" t="n">
-        <v>5.921672302490009</v>
+        <v>5.923690951941797</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>5.923690951941797</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>1429000</v>
+      </c>
+      <c r="C420" t="n">
+        <v>574797</v>
+      </c>
+      <c r="D420" t="n">
+        <v>1313878</v>
+      </c>
+      <c r="E420" t="n">
+        <v>1389647</v>
+      </c>
+      <c r="F420" t="n">
+        <v>1378487</v>
+      </c>
+      <c r="G420" t="n">
+        <v>1360671</v>
+      </c>
+      <c r="H420" t="n">
+        <v>5.971364893944052</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>1524000</v>
+        <v>1486000</v>
       </c>
       <c r="C421" t="n">
-        <v>203809</v>
+        <v>871236</v>
       </c>
       <c r="D421" t="n">
-        <v>1314443</v>
+        <v>1317790</v>
       </c>
       <c r="E421" t="n">
-        <v>1391871</v>
+        <v>1396114</v>
       </c>
       <c r="F421" t="n">
-        <v>1397895</v>
+        <v>1414137</v>
       </c>
       <c r="G421" t="n">
-        <v>1368070</v>
+        <v>1376014</v>
       </c>
       <c r="H421" t="n">
-        <v>6.009273491136387</v>
+        <v>6.04997438262117</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>6.04997438262117</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>1507000</v>
+      </c>
+      <c r="C422" t="n">
+        <v>482248</v>
+      </c>
+      <c r="D422" t="n">
+        <v>1317944</v>
+      </c>
+      <c r="E422" t="n">
+        <v>1400086</v>
+      </c>
+      <c r="F422" t="n">
+        <v>1432431</v>
+      </c>
+      <c r="G422" t="n">
+        <v>1383487</v>
+      </c>
+      <c r="H422" t="n">
+        <v>6.088262117020187</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>6.088262117020187</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>1499000</v>
+      </c>
+      <c r="C423" t="n">
+        <v>619786</v>
+      </c>
+      <c r="D423" t="n">
+        <v>1329548</v>
+      </c>
+      <c r="E423" t="n">
+        <v>1413912</v>
+      </c>
+      <c r="F423" t="n">
+        <v>1456844</v>
+      </c>
+      <c r="G423" t="n">
+        <v>1400101</v>
+      </c>
+      <c r="H423" t="n">
+        <v>6.17338354339584</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>6.17338354339584</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>1528000</v>
+      </c>
+      <c r="C424" t="n">
+        <v>549141</v>
+      </c>
+      <c r="D424" t="n">
+        <v>1348141</v>
+      </c>
+      <c r="E424" t="n">
+        <v>1419327</v>
+      </c>
+      <c r="F424" t="n">
+        <v>1488740</v>
+      </c>
+      <c r="G424" t="n">
+        <v>1418736</v>
+      </c>
+      <c r="H424" t="n">
+        <v>6.268859514294498</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>6.268859514294498</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>1513000</v>
+      </c>
+      <c r="C425" t="n">
+        <v>492946</v>
+      </c>
+      <c r="D425" t="n">
+        <v>1379511</v>
+      </c>
+      <c r="E425" t="n">
+        <v>1420376</v>
+      </c>
+      <c r="F425" t="n">
+        <v>1504093</v>
+      </c>
+      <c r="G425" t="n">
+        <v>1434660</v>
+      </c>
+      <c r="H425" t="n">
+        <v>6.350445742391639</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>6.350445742391639</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>1561000</v>
+      </c>
+      <c r="C426" t="n">
+        <v>612228</v>
+      </c>
+      <c r="D426" t="n">
+        <v>1383455</v>
+      </c>
+      <c r="E426" t="n">
+        <v>1427559</v>
+      </c>
+      <c r="F426" t="n">
+        <v>1522452</v>
+      </c>
+      <c r="G426" t="n">
+        <v>1444489</v>
+      </c>
+      <c r="H426" t="n">
+        <v>6.400804385695255</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>1581000</v>
+      </c>
+      <c r="C427" t="n">
+        <v>480933</v>
+      </c>
+      <c r="D427" t="n">
+        <v>1386771</v>
+      </c>
+      <c r="E427" t="n">
+        <v>1435320</v>
+      </c>
+      <c r="F427" t="n">
+        <v>1535377</v>
+      </c>
+      <c r="G427" t="n">
+        <v>1452489</v>
+      </c>
+      <c r="H427" t="n">
+        <v>6.441792191822933</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>6.441792191822933</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>1675000</v>
+      </c>
+      <c r="C428" t="n">
+        <v>762179</v>
+      </c>
+      <c r="D428" t="n">
+        <v>1419560</v>
+      </c>
+      <c r="E428" t="n">
+        <v>1459375</v>
+      </c>
+      <c r="F428" t="n">
+        <v>1579887</v>
+      </c>
+      <c r="G428" t="n">
+        <v>1486274</v>
+      </c>
+      <c r="H428" t="n">
+        <v>6.614888820575879</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>6.614888820575879</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>1604000</v>
+      </c>
+      <c r="C429" t="n">
+        <v>578369</v>
+      </c>
+      <c r="D429" t="n">
+        <v>1428890</v>
+      </c>
+      <c r="E429" t="n">
+        <v>1467431</v>
+      </c>
+      <c r="F429" t="n">
+        <v>1594388</v>
+      </c>
+      <c r="G429" t="n">
+        <v>1496903</v>
+      </c>
+      <c r="H429" t="n">
+        <v>6.669346244492264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>6.669346244492264</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>1546000</v>
+      </c>
+      <c r="C430" t="n">
+        <v>534894</v>
+      </c>
+      <c r="D430" t="n">
+        <v>1431342</v>
+      </c>
+      <c r="E430" t="n">
+        <v>1477659</v>
+      </c>
+      <c r="F430" t="n">
+        <v>1599184</v>
+      </c>
+      <c r="G430" t="n">
+        <v>1502728</v>
+      </c>
+      <c r="H430" t="n">
+        <v>6.699190490828978</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>6.699190490828978</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>1487000</v>
+      </c>
+      <c r="C431" t="n">
+        <v>608864</v>
+      </c>
+      <c r="D431" t="n">
+        <v>1444636</v>
+      </c>
+      <c r="E431" t="n">
+        <v>1490978</v>
+      </c>
+      <c r="F431" t="n">
+        <v>1584033</v>
+      </c>
+      <c r="G431" t="n">
+        <v>1506549</v>
+      </c>
+      <c r="H431" t="n">
+        <v>6.71876729173071</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>6.71876729173071</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>1363000</v>
+      </c>
+      <c r="C432" t="n">
+        <v>923313</v>
+      </c>
+      <c r="D432" t="n">
+        <v>1438652</v>
+      </c>
+      <c r="E432" t="n">
+        <v>1479763</v>
+      </c>
+      <c r="F432" t="n">
+        <v>1524571</v>
+      </c>
+      <c r="G432" t="n">
+        <v>1480995</v>
+      </c>
+      <c r="H432" t="n">
+        <v>6.587841992007378</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>6.587841992007378</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>1374000</v>
+      </c>
+      <c r="C433" t="n">
+        <v>540310</v>
+      </c>
+      <c r="D433" t="n">
+        <v>1432236</v>
+      </c>
+      <c r="E433" t="n">
+        <v>1480412</v>
+      </c>
+      <c r="F433" t="n">
+        <v>1463044</v>
+      </c>
+      <c r="G433" t="n">
+        <v>1458564</v>
+      </c>
+      <c r="H433" t="n">
+        <v>6.472917307101137</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>6.472917307101137</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>1163000</v>
+      </c>
+      <c r="C434" t="n">
+        <v>1172213</v>
+      </c>
+      <c r="D434" t="n">
+        <v>1419421</v>
+      </c>
+      <c r="E434" t="n">
+        <v>1452312</v>
+      </c>
+      <c r="F434" t="n">
+        <v>1348418</v>
+      </c>
+      <c r="G434" t="n">
+        <v>1406717</v>
+      </c>
+      <c r="H434" t="n">
+        <v>6.207280459063429</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>6.207280459063429</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>1188000</v>
+      </c>
+      <c r="C435" t="n">
+        <v>700433</v>
+      </c>
+      <c r="D435" t="n">
+        <v>1413021</v>
+      </c>
+      <c r="E435" t="n">
+        <v>1439135</v>
+      </c>
+      <c r="F435" t="n">
+        <v>1293148</v>
+      </c>
+      <c r="G435" t="n">
+        <v>1381768</v>
+      </c>
+      <c r="H435" t="n">
+        <v>6.079454862178502</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>6.079454862178502</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>1170000</v>
+      </c>
+      <c r="C436" t="n">
+        <v>781716</v>
+      </c>
+      <c r="D436" t="n">
+        <v>1404792</v>
+      </c>
+      <c r="E436" t="n">
+        <v>1428400</v>
+      </c>
+      <c r="F436" t="n">
+        <v>1241109</v>
+      </c>
+      <c r="G436" t="n">
+        <v>1358100</v>
+      </c>
+      <c r="H436" t="n">
+        <v>5.958192437749769</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>5.958192437749769</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="C437" t="n">
+        <v>680203</v>
+      </c>
+      <c r="D437" t="n">
+        <v>1398050</v>
+      </c>
+      <c r="E437" t="n">
+        <v>1412858</v>
+      </c>
+      <c r="F437" t="n">
+        <v>1196949</v>
+      </c>
+      <c r="G437" t="n">
+        <v>1335952</v>
+      </c>
+      <c r="H437" t="n">
+        <v>5.844717696485295</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>5.844717696485295</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>1168000</v>
+      </c>
+      <c r="C438" t="n">
+        <v>573864</v>
+      </c>
+      <c r="D438" t="n">
+        <v>1394961</v>
+      </c>
+      <c r="E438" t="n">
+        <v>1400339</v>
+      </c>
+      <c r="F438" t="n">
+        <v>1168222</v>
+      </c>
+      <c r="G438" t="n">
+        <v>1321174</v>
+      </c>
+      <c r="H438" t="n">
+        <v>5.769002971615945</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>5.769002971615945</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>1145000</v>
+      </c>
+      <c r="C439" t="n">
+        <v>786464</v>
+      </c>
+      <c r="D439" t="n">
+        <v>1387053</v>
+      </c>
+      <c r="E439" t="n">
+        <v>1377153</v>
+      </c>
+      <c r="F439" t="n">
+        <v>1164775</v>
+      </c>
+      <c r="G439" t="n">
+        <v>1309661</v>
+      </c>
+      <c r="H439" t="n">
+        <v>5.710016395122451</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>5.710016395122451</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>1122000</v>
+      </c>
+      <c r="C440" t="n">
+        <v>732037</v>
+      </c>
+      <c r="D440" t="n">
+        <v>1379472</v>
+      </c>
+      <c r="E440" t="n">
+        <v>1356592</v>
+      </c>
+      <c r="F440" t="n">
+        <v>1151389</v>
+      </c>
+      <c r="G440" t="n">
+        <v>1295818</v>
+      </c>
+      <c r="H440" t="n">
+        <v>5.639092120094272</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>5.639092120094272</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>1118000</v>
+      </c>
+      <c r="C441" t="n">
+        <v>461368</v>
+      </c>
+      <c r="D441" t="n">
+        <v>1377201</v>
+      </c>
+      <c r="E441" t="n">
+        <v>1347850</v>
+      </c>
+      <c r="F441" t="n">
+        <v>1142126</v>
+      </c>
+      <c r="G441" t="n">
+        <v>1289059</v>
+      </c>
+      <c r="H441" t="n">
+        <v>5.604462547392151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>5.604462547392151</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>1201000</v>
+      </c>
+      <c r="C442" t="n">
+        <v>747688</v>
+      </c>
+      <c r="D442" t="n">
+        <v>1371611</v>
+      </c>
+      <c r="E442" t="n">
+        <v>1339618</v>
+      </c>
+      <c r="F442" t="n">
+        <v>1152807</v>
+      </c>
+      <c r="G442" t="n">
+        <v>1288012</v>
+      </c>
+      <c r="H442" t="n">
+        <v>5.599098268265191</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>5.599098268265191</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>1306000</v>
+      </c>
+      <c r="C443" t="n">
+        <v>899774</v>
+      </c>
+      <c r="D443" t="n">
+        <v>1367611</v>
+      </c>
+      <c r="E443" t="n">
+        <v>1330144</v>
+      </c>
+      <c r="F443" t="n">
+        <v>1188404</v>
+      </c>
+      <c r="G443" t="n">
+        <v>1295386</v>
+      </c>
+      <c r="H443" t="n">
+        <v>5.636878778563378</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>5.636878778563378</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>1293000</v>
+      </c>
+      <c r="C444" t="n">
+        <v>1123468</v>
+      </c>
+      <c r="D444" t="n">
+        <v>1364357</v>
+      </c>
+      <c r="E444" t="n">
+        <v>1319549</v>
+      </c>
+      <c r="F444" t="n">
+        <v>1226656</v>
+      </c>
+      <c r="G444" t="n">
+        <v>1303521</v>
+      </c>
+      <c r="H444" t="n">
+        <v>5.678558253919459</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전기_일별_기준주가.xlsx
+++ b/data/삼성전기_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>5.678558253919459</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>1196000</v>
+      </c>
+      <c r="C445" t="n">
+        <v>840776</v>
+      </c>
+      <c r="D445" t="n">
+        <v>1359036</v>
+      </c>
+      <c r="E445" t="n">
+        <v>1305847</v>
+      </c>
+      <c r="F445" t="n">
+        <v>1239138</v>
+      </c>
+      <c r="G445" t="n">
+        <v>1301340</v>
+      </c>
+      <c r="H445" t="n">
+        <v>5.667383953273901</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
